--- a/Excel/Version 1/Bakery Products.xlsx
+++ b/Excel/Version 1/Bakery Products.xlsx
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E2" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E2">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JDMWXXVESSZDANI</v>
+        <v>KBLFFYMMBUTLRAY</v>
       </c>
       <c r="F2" s="9">
         <v>129</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E3" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E3">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>WMUGXFXPEWOXQHP</v>
+        <v>LJRLBVVEPCPGSNJ</v>
       </c>
       <c r="F3" s="9">
         <v>129</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E4" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E4">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>DWYMNEZKWWRUDGZ</v>
+        <v>OINNXFHOSOPROHV</v>
       </c>
       <c r="F4" s="9">
         <v>129</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E5" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E5">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>YBAJSWAJPKRGFTN</v>
+        <v>OLPZNHGQXMAEWZW</v>
       </c>
       <c r="F5" s="9">
         <v>129</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E6" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E6">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CVNOBLDJTSXNXEH</v>
+        <v>KHZDYYQFMJSHEJD</v>
       </c>
       <c r="F6" s="9">
         <v>129</v>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E7" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E7">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>AOHWLHJMGWPWHPL</v>
+        <v>SOHKDRRKGXIAFBF</v>
       </c>
       <c r="F7" s="9">
         <v>129</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="E8" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E8">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FTVDRIIPCJZBIPC</v>
+        <v>WDUSYXNCXDVEMOI</v>
       </c>
       <c r="F8" s="9">
         <v>129</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E9" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E9">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VIOBDXTOIGHQGBK</v>
+        <v>APHGZITVUVCPARR</v>
       </c>
       <c r="F9" s="9">
         <v>129</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="E10" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E10">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>WWXYHJENVIPTHGK</v>
+        <v>MAZMLPDMVDZYSDO</v>
       </c>
       <c r="F10" s="9">
         <v>129</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="E11" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E11">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>DXZXUOKADLQXZWF</v>
+        <v>FVLALAMXWJIEXQH</v>
       </c>
       <c r="F11" s="9">
         <v>129</v>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E12" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E12">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>SQGXTMHBCFXTXDZ</v>
+        <v>CYUTYHJAETTNGGO</v>
       </c>
       <c r="F12" s="9">
         <v>129</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="E13" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E13">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>UZIMZNEYZGZBRJW</v>
+        <v>VRBPXSCSTPGPMDI</v>
       </c>
       <c r="F13" s="9">
         <v>129</v>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="E14" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E14">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>MNXYFRJZQRRQTXH</v>
+        <v>MHUXXTITEMKKGTQ</v>
       </c>
       <c r="F14" s="9">
         <v>129</v>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E15" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E15">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>LOUBESGTCWSALJW</v>
+        <v>ZFDIUIGRAABRYJT</v>
       </c>
       <c r="F15" s="9">
         <v>129</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E16" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E16">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>IUFZNZNJNIJYTEY</v>
+        <v>BXSZARIXDJBVTWX</v>
       </c>
       <c r="F16" s="9">
         <v>129</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="E17" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E17">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ATSHEMMTRVYMBPV</v>
+        <v>UJWZAIORTLSDBBJ</v>
       </c>
       <c r="F17" s="9">
         <v>129</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="E18" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E18">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>QVVXTTFAWUKTEAU</v>
+        <v>QHJHDXLDWJOANHD</v>
       </c>
       <c r="F18" s="9">
         <v>129</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E19" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E19">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>WNKRCSGKUBWVUSX</v>
+        <v>VWTAEALWPDHGODE</v>
       </c>
       <c r="F19" s="9">
         <v>129</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E20" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E20">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>AQOXMYZSCXNMJXI</v>
+        <v>REKGVWPFBEVIYFB</v>
       </c>
       <c r="F20" s="9">
         <v>129</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E21" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E21">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VRFDKZNSOISTYSO</v>
+        <v>CXPSHJSXGAYMIDL</v>
       </c>
       <c r="F21" s="9">
         <v>129</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="E22" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E22">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>HKHXADNOKTGWQRO</v>
+        <v>IAUDOXAVNMIHXCF</v>
       </c>
       <c r="F22" s="9">
         <v>129</v>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="E23" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E23">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>OPYGVJJOSMMLTJZ</v>
+        <v>RWJZLRYMVGULWIJ</v>
       </c>
       <c r="F23" s="9">
         <v>129</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E24" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E24">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VREYCNXGRFZJOKW</v>
+        <v>NDHZKFGNRRZHHCI</v>
       </c>
       <c r="F24" s="9">
         <v>129</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="E25" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E25">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PQFWPMWCHIPORZS</v>
+        <v>ZFNBUZMJUEOJCQI</v>
       </c>
       <c r="F25" s="9">
         <v>129</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="E26" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E26">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>QKOGVZTRVEYERXD</v>
+        <v>ZUHBJHNXLCXQMJP</v>
       </c>
       <c r="F26" s="9">
         <v>129</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="E27" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E27">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>NKFBQURRTLPJLAG</v>
+        <v>JTEHXIPPRUZMNUE</v>
       </c>
       <c r="F27" s="9">
         <v>129</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E28" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E28">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GYMQBFVZSLLXMKU</v>
+        <v>IUSNPKXKNQMDFMW</v>
       </c>
       <c r="F28" s="9">
         <v>129</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="E29" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E29">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>EDORZRFDIILJTGK</v>
+        <v>HLEMTJWTUOXJOXK</v>
       </c>
       <c r="F29" s="9">
         <v>129</v>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E30" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E30">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XXPLVGYOYNGQZZA</v>
+        <v>CZVTUBZVASLRALG</v>
       </c>
       <c r="F30" s="9">
         <v>129</v>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E31" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E31">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>IZPTFMXCJECVDAL</v>
+        <v>EZLDQJJCOJREDPX</v>
       </c>
       <c r="F31" s="9">
         <v>129</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="E32" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E32">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>LSEUOWHFXJRUJTR</v>
+        <v>ZUKPLNMSRHMPIHK</v>
       </c>
       <c r="F32" s="9">
         <v>129</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E33" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E33">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ZSECLANRGYGUQRS</v>
+        <v>TPXCRTTWMONFHFD</v>
       </c>
       <c r="F33" s="9">
         <v>129</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E34" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E34">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>WVWLDEHBDMBHYYT</v>
+        <v>ZPIXUSKSMIWYZMC</v>
       </c>
       <c r="F34" s="9">
         <v>129</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E35" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E35">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GGSLHIMFXARTUOG</v>
+        <v>YGUPIKRVNHBBAQB</v>
       </c>
       <c r="F35" s="9">
         <v>129</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="E36" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E36">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JQZHWQJYWKBCUXV</v>
+        <v>JKZRBJGSMEXRGNR</v>
       </c>
       <c r="F36" s="9">
         <v>129</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E37" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E37">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FASPGMMKUDCHZNM</v>
+        <v>URQKFCEFARHTDZR</v>
       </c>
       <c r="F37" s="9">
         <v>129</v>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="E38" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E38">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>EUBLDJSMHKFZEXY</v>
+        <v>TCRDEUNMBRHYFJN</v>
       </c>
       <c r="F38" s="9">
         <v>129</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="E39" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E39">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>SBHMSECVIMFSFIY</v>
+        <v>RXSWZSIJRJGFKFQ</v>
       </c>
       <c r="F39" s="9">
         <v>129</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E40" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E40">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TXAHOJSOGHOMTZF</v>
+        <v>ZXHUVGUELOSYMOE</v>
       </c>
       <c r="F40" s="9">
         <v>129</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E41" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E41">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>OZGIDUCDOEFEXSZ</v>
+        <v>YASLYJSYFKWZMCQ</v>
       </c>
       <c r="F41" s="9">
         <v>129</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="E42" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E42">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>RZQMERPRAXXDIST</v>
+        <v>FFNPEDTLERHDRZY</v>
       </c>
       <c r="F42" s="9">
         <v>129</v>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E43" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E43">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JIKDOZJEYRVMXOC</v>
+        <v>ZXBCJJRNRCAUHWM</v>
       </c>
       <c r="F43" s="9">
         <v>129</v>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="E44" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E44">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VQNSZCZLFZEJOJL</v>
+        <v>DBPBCNTMASLZGCG</v>
       </c>
       <c r="F44" s="9">
         <v>129</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E45" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E45">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>KTRQNMEDKIRMSJP</v>
+        <v>AMKWMPEBAKSJXAV</v>
       </c>
       <c r="F45" s="9">
         <v>129</v>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="E46" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E46">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XYHISCZQBPKWOLX</v>
+        <v>HBWJFJROJSDMENV</v>
       </c>
       <c r="F46" s="9">
         <v>129</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E47" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E47">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>LZHFVQWOIOVQRAY</v>
+        <v>ZZJGOWZPAVVQAXM</v>
       </c>
       <c r="F47" s="9">
         <v>129</v>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E48" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E48">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JTLKRXITLVWDSWF</v>
+        <v>AJEQMLUDVVVYEKW</v>
       </c>
       <c r="F48" s="9">
         <v>129</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E49" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E49">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FSQALLILQJGHTYN</v>
+        <v>ORSESQBTSFACIQP</v>
       </c>
       <c r="F49" s="9">
         <v>129</v>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="E50" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E50">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>BLFBRCTCPTLQWXB</v>
+        <v>EOABIYZIUEWQTFS</v>
       </c>
       <c r="F50" s="9">
         <v>129</v>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E51" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E51">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TWFQTTNNPEFUBGK</v>
+        <v>QECSIGXENIHEYRZ</v>
       </c>
       <c r="F51" s="9">
         <v>129</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E52" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E52">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JCUUROMYACJEJJP</v>
+        <v>IICVMBMIMTCOSFZ</v>
       </c>
       <c r="F52" s="9">
         <v>129</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="E53" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E53">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>MCFFKMUMCONGTBM</v>
+        <v>APYPVKRMPIKYCDE</v>
       </c>
       <c r="F53" s="9">
         <v>129</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E54" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E54">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FRSVKSOLTWTIENH</v>
+        <v>MPNIGAYNYTENBTF</v>
       </c>
       <c r="F54" s="9">
         <v>129</v>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E55" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E55">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JWGJWCTLHWRGLFQ</v>
+        <v>PDSNNOIXAIKJQOM</v>
       </c>
       <c r="F55" s="9">
         <v>129</v>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="E56" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E56">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XVCKVVIHVWSJHFX</v>
+        <v>WQGPWADDVMKADKH</v>
       </c>
       <c r="F56" s="9">
         <v>129</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="E57" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E57">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VFEQLVJRYGLESNZ</v>
+        <v>YCYVWQLVYHMGDTV</v>
       </c>
       <c r="F57" s="9">
         <v>129</v>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E58" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E58">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ZBAJUMQQTVLMRUH</v>
+        <v>PMTBFDFMLPHFWZR</v>
       </c>
       <c r="F58" s="9">
         <v>129</v>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="E59" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E59">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>QXWVQNUMDRTNJLD</v>
+        <v>VUISPHSZFEGZNLG</v>
       </c>
       <c r="F59" s="9">
         <v>129</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="E60" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E60">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>IGKYIETWEQELXJP</v>
+        <v>XXIDJVZSVYQCIWO</v>
       </c>
       <c r="F60" s="9">
         <v>129</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E61" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E61">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XBHXTSOLCCUFSTU</v>
+        <v>YBMQWZVKMXOIKEQ</v>
       </c>
       <c r="F61" s="9">
         <v>129</v>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E62" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E62">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TZGKHSWOHQVCGZE</v>
+        <v>CQSFMEEMWQYSAWU</v>
       </c>
       <c r="F62" s="9">
         <v>129</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="E63" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E63">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>BUNSVYMJYMLDGAP</v>
+        <v>PSJZTRDQVIVGSMR</v>
       </c>
       <c r="F63" s="9">
         <v>129</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="E64" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E64">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TTXTYYTGIFQBUNG</v>
+        <v>KRNRXOKZGMGHUZA</v>
       </c>
       <c r="F64" s="9">
         <v>129</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="E65" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E65">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>NLLIAAWQLTHMNMZ</v>
+        <v>GNEXRJCPSRDNUDV</v>
       </c>
       <c r="F65" s="9">
         <v>129</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="E66" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E66">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GZVGQIUTONKWHQO</v>
+        <v>DTKLAYZOZIAAXFM</v>
       </c>
       <c r="F66" s="9">
         <v>129</v>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E67" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E67">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XSBIJDLPJSCISRQ</v>
+        <v>XQEFMPYCWSYPSGP</v>
       </c>
       <c r="F67" s="9">
         <v>129</v>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="E68" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E68">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>BMPEFWGOTMJSGVG</v>
+        <v>AMYYFDNFYPPWPDG</v>
       </c>
       <c r="F68" s="9">
         <v>129</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E69" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E69">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GVEXFJABMCHZYUL</v>
+        <v>ADKJKBNBXQQCRQB</v>
       </c>
       <c r="F69" s="9">
         <v>129</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="E70" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E70">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ZUKEHEDGPNWANME</v>
+        <v>ARBWPYMNPRQPEHM</v>
       </c>
       <c r="F70" s="9">
         <v>129</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="E71" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E71">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JMPIXUAVMQMILSE</v>
+        <v>QERBWPEWCNIXANY</v>
       </c>
       <c r="F71" s="9">
         <v>129</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="E72" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E72">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PMUROBDNTRJMMGD</v>
+        <v>KKALBJDMZXOFAIU</v>
       </c>
       <c r="F72" s="9">
         <v>129</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E73" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E73">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GHWKYNLQYMSWASK</v>
+        <v>MWAZJOYHDEYCPWP</v>
       </c>
       <c r="F73" s="9">
         <v>129</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E74" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E74">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PYANZUCFQHOFVWJ</v>
+        <v>JLXVMPOLXPRXUTH</v>
       </c>
       <c r="F74" s="9">
         <v>129</v>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="E75" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E75">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>AKWYAQXTVIWMGIB</v>
+        <v>PYEFFGIUNDAIBCF</v>
       </c>
       <c r="F75" s="9">
         <v>129</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="E76" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E76">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CHWIOXGRCASCJGY</v>
+        <v>BWOKGGYNZBIMSFD</v>
       </c>
       <c r="F76" s="9">
         <v>129</v>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E77" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E77">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CHLDVIKWKQCRDJV</v>
+        <v>QUUTERBMABJBXLT</v>
       </c>
       <c r="F77" s="9">
         <v>129</v>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="E78" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E78">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>EEXNUVTLSMPTJLQ</v>
+        <v>YJWBKCQIGGSNIDD</v>
       </c>
       <c r="F78" s="9">
         <v>129</v>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="E79" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E79">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>KXXAXWQPYUKBIRE</v>
+        <v>SJWNZCRKADENLPU</v>
       </c>
       <c r="F79" s="9">
         <v>129</v>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E80" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E80">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ODPRVSBVZRIUYPH</v>
+        <v>ZVGSNTOKYUDWTVH</v>
       </c>
       <c r="F80" s="9">
         <v>129</v>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E81" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E81">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TGYMOUQRBBUNDVR</v>
+        <v>KTVEJKMPTSKMHGX</v>
       </c>
       <c r="F81" s="9">
         <v>129</v>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="E82" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E82">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TVDXPIHNYDLITGS</v>
+        <v>OFSEGRPWZBJSEET</v>
       </c>
       <c r="F82" s="9">
         <v>129</v>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="E83" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E83">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>YXDAYKOBNDOBRYK</v>
+        <v>NWENIRRQJMNOJBA</v>
       </c>
       <c r="F83" s="9">
         <v>129</v>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="E84" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E84">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XCTFLOIOYMUVDSC</v>
+        <v>JYOZHDBLPLDRVLG</v>
       </c>
       <c r="F84" s="9">
         <v>129</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="E85" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E85">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>EFMHNMOMXZODTEX</v>
+        <v>AREZJZQNDOYUPYF</v>
       </c>
       <c r="F85" s="9">
         <v>129</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E86" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E86">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>UGTLUVIBYRAUCTY</v>
+        <v>CMPHGJDPJZFMJUV</v>
       </c>
       <c r="F86" s="9">
         <v>129</v>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="E87" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E87">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>YMBQXLRHWLQDLYX</v>
+        <v>GJBHGKIWAHQOYNU</v>
       </c>
       <c r="F87" s="9">
         <v>129</v>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="E88" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E88">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CDDBGWBYJVFSCAR</v>
+        <v>TCJZQYQUJRENLCO</v>
       </c>
       <c r="F88" s="9">
         <v>129</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="E89" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E89">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>TZHATCXKDQKXKUC</v>
+        <v>YAYRTLIVGCFOILV</v>
       </c>
       <c r="F89" s="9">
         <v>129</v>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="E90" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E90">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>HDIRBVQHAIDUSJJ</v>
+        <v>LKUXOUYXPMBCWLH</v>
       </c>
       <c r="F90" s="9">
         <v>129</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E91" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E91">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PXMWVNFSROBAHBG</v>
+        <v>YUXOEIHXJZDNZBT</v>
       </c>
       <c r="F91" s="9">
         <v>129</v>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="E92" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E92">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FETHZQTLXJMWSDZ</v>
+        <v>KGQBOFNOIPKJWLN</v>
       </c>
       <c r="F92" s="9">
         <v>129</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="E93" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E93">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>SIMOCWRPRZJGKON</v>
+        <v>BQVOIMJEEQNAKET</v>
       </c>
       <c r="F93" s="9">
         <v>129</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="E94" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E94">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JPIXPZPROIENDJL</v>
+        <v>PDQPPEFLGRSPMCH</v>
       </c>
       <c r="F94" s="9">
         <v>129</v>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="E95" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E95">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>JOSOVMJTBCCRSCD</v>
+        <v>SQWKBMINHBJEAJF</v>
       </c>
       <c r="F95" s="9">
         <v>129</v>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="E96" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E96">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ZTAUUFZPFHPVGPG</v>
+        <v>HZOZYIVGONDYBEU</v>
       </c>
       <c r="F96" s="9">
         <v>129</v>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E97" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E97">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GLVUQWTIHOWNUPN</v>
+        <v>OGRXEFWDWWGLTEX</v>
       </c>
       <c r="F97" s="9">
         <v>129</v>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="E98" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E98">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ZGGRCDUESAMPSJF</v>
+        <v>LYDJAYLAXWTMVPA</v>
       </c>
       <c r="F98" s="9">
         <v>129</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E99" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E99">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>NAOSEOFWJIWYDTT</v>
+        <v>VMRQNQCCVMQPDQA</v>
       </c>
       <c r="F99" s="9">
         <v>129</v>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="E100" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E100">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>EHTXAVHXMZEZCHZ</v>
+        <v>IENJUHVCLBGMCAC</v>
       </c>
       <c r="F100" s="9">
         <v>129</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="E101" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E101">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FWHDAPPAPHRGWFI</v>
+        <v>JQWMQYGKFPQOYML</v>
       </c>
       <c r="F101" s="9">
         <v>129</v>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E102" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E102">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>FPGNRYLVOAPIFJW</v>
+        <v>PYDYVOTSMEURCIX</v>
       </c>
       <c r="F102" s="9">
         <v>129</v>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E103" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E103">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>BYYPSZHPEBCAGHT</v>
+        <v>KEVRQOMKOHCRBFK</v>
       </c>
       <c r="F103" s="9">
         <v>129</v>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E104" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E104">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>XSGAEFIIMPCZYWM</v>
+        <v>XCHGMMLHHHLDXJJ</v>
       </c>
       <c r="F104" s="9">
         <v>129</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="E105" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E105">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>HAGZCATKYAIGOZE</v>
+        <v>ILKZMDHXTUPWRHQ</v>
       </c>
       <c r="F105" s="9">
         <v>129</v>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="E106" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E106">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CBZYMWMLGTWMSCP</v>
+        <v>HLUZOENJZCNVFXI</v>
       </c>
       <c r="F106" s="9">
         <v>129</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="E107" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E107">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>WEEBQNOFIYLTEHQ</v>
+        <v>UMHRGQCFWQMOLJC</v>
       </c>
       <c r="F107" s="9">
         <v>129</v>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="E108" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E108">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>VADNSTURSKYDSRN</v>
+        <v>PLIIRPJPWRFDWMC</v>
       </c>
       <c r="F108" s="9">
         <v>129</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="E109" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E109">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>ONIFKDRFHZUCPSY</v>
+        <v>AZXRSMZYIFPZANA</v>
       </c>
       <c r="F109" s="9">
         <v>129</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="E110" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E110">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>NSZNSQIAPGZKUCQ</v>
+        <v>TLUWHDABXODEBBA</v>
       </c>
       <c r="F110" s="9">
         <v>129</v>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="E111" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E111">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CAGFOVVGWPVCBLL</v>
+        <v>RGPGDBHWBCKKJWT</v>
       </c>
       <c r="F111" s="9">
         <v>129</v>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="E112" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E112">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PVATXJOKAWEXAQB</v>
+        <v>VVHPWLYPNTPBRCI</v>
       </c>
       <c r="F112" s="9">
         <v>129</v>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E113" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E113">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>CPMWDKHZJHNUXPF</v>
+        <v>VXPMTDDGJVAMYOL</v>
       </c>
       <c r="F113" s="9">
         <v>129</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="E114" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E114">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>GSFMFNUFWIWMWSU</v>
+        <v>RPZNJHCOYHDMBEM</v>
       </c>
       <c r="F114" s="9">
         <v>129</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="E115" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E115">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>PVYSAMDIDBOMBYG</v>
+        <v>LTDIIMRUZCMGNCS</v>
       </c>
       <c r="F115" s="9">
         <v>129</v>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="E116" s="6" t="str" cm="1">
         <f ca="1" t="array" ref="E116">_xlfn.TEXTJOIN("",TRUE,CHAR(RANDBETWEEN(65,90+0*_xlfn.SEQUENCE(15))))</f>
-        <v>AQJISLBNOFOZATD</v>
+        <v>OVOBIZCOKMWMSGL</v>
       </c>
       <c r="F116" s="9">
         <v>129</v>
